--- a/LubanConfig/MiniTemplate/Datas/基础数据/#关卡设计表.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/基础数据/#关卡设计表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="25">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -114,6 +114,10 @@
   </si>
   <si>
     <t>雪山</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阵容强度范围：3——42</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -647,6 +651,9 @@
       <c r="E11" s="4" t="s">
         <v>21</v>
       </c>
+      <c r="H11" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B12" s="4">
